--- a/Bai1.2_TestCase.xlsx
+++ b/Bai1.2_TestCase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Software-Testing\Buoi7\1150080143_VoAnhKiet_CNPM2_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6292180D-F4E4-46FE-8186-E3AEA4A88E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE0330C-4BD3-4671-8FF6-A587C5113236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,9 +237,6 @@
     <t>Các bước thực hiện</t>
   </si>
   <si>
-    <t>KIỂM THỬ LOGIC ĐĂNG KÝ</t>
-  </si>
-  <si>
     <t>Chưa test</t>
   </si>
   <si>
@@ -680,6 +677,9 @@
   <si>
     <t>B1: Gửi request yêu cầu chuyển 50k (Phí 16.5k).
 B2: Kiểm tra logic chặn giao dịch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIỂM THỬ </t>
   </si>
 </sst>
 </file>
@@ -893,6 +893,60 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -902,68 +956,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1265,48 +1265,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="7"/>
     </row>
@@ -1318,13 +1318,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B13" s="7"/>
     </row>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
@@ -1441,33 +1441,33 @@
         <v>31</v>
       </c>
       <c r="J29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="L29" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="L29" s="10" t="s">
+      <c r="M29" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="M29" s="10" t="s">
+      <c r="N29" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="N29" s="10" t="s">
+      <c r="O29" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="O29" s="10" t="s">
+      <c r="P29" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="P29" s="10" t="s">
+      <c r="Q29" s="10" t="s">
         <v>99</v>
-      </c>
-      <c r="Q29" s="10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>32</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>32</v>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>32</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>32</v>
@@ -1681,26 +1681,26 @@
       <c r="A34" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="33"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="36"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>35</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="36" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="37" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="38" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="39" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B39" s="10"/>
       <c r="C39" s="10"/>
@@ -1837,7 +1837,7 @@
     </row>
     <row r="40" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>35</v>
@@ -1874,206 +1874,206 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="34" t="s">
+      <c r="A47" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B47" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="G47" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="H47" s="35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="31" t="s">
+      <c r="B48" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="F48" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G48" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="H48" s="35" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="31" t="s">
+      <c r="B49" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F49" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" s="29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="B49" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="D49" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="E49" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F49" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G49" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="H49" s="35" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B50" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="F50" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G50" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="H50" s="35" t="s">
+      <c r="B50" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="29" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B53" s="29"/>
+      <c r="C53" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="31" t="s">
+      <c r="D53" s="29"/>
+      <c r="E53" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+    </row>
+    <row r="54" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="B53" s="35"/>
-      <c r="C53" s="35" t="s">
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35" t="s">
+      <c r="E54" s="29"/>
+      <c r="F54" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-    </row>
-    <row r="54" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="31" t="s">
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+    </row>
+    <row r="55" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35" t="s">
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-    </row>
-    <row r="55" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="31" t="s">
+      <c r="H55" s="29"/>
+    </row>
+    <row r="56" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="35"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="H55" s="35"/>
-    </row>
-    <row r="56" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35" t="s">
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2084,42 +2084,42 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2137,20 +2137,20 @@
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultColWidth="32" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32" style="19"/>
-    <col min="2" max="2" width="35.33203125" style="19" customWidth="1"/>
-    <col min="3" max="16384" width="32" style="19"/>
+    <col min="1" max="1" width="32" style="15"/>
+    <col min="2" max="2" width="35.33203125" style="15" customWidth="1"/>
+    <col min="3" max="16384" width="32" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="A1" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
@@ -2167,41 +2167,41 @@
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="16" t="s">
         <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="17" t="s">
         <v>54</v>
       </c>
       <c r="G4" s="5"/>
@@ -2209,7 +2209,7 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2220,16 +2220,16 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>55</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="19">
         <v>46084</v>
       </c>
       <c r="E6" s="5"/>
@@ -2240,7 +2240,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="25"/>
+      <c r="D7" s="20"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
@@ -2248,10 +2248,10 @@
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="30" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="4"/>
@@ -2267,18 +2267,18 @@
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="37">
+      <c r="A9" s="31">
         <v>1</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>118</v>
+      <c r="B9" s="26" t="s">
+        <v>117</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="37">
+      <c r="D9" s="31">
         <v>1</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>121</v>
+      <c r="E9" s="27" t="s">
+        <v>120</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -2286,18 +2286,18 @@
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37">
+      <c r="A10" s="31">
         <v>2</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>119</v>
+      <c r="B10" s="26" t="s">
+        <v>118</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="37">
+      <c r="D10" s="31">
         <v>2</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>122</v>
+      <c r="E10" s="27" t="s">
+        <v>121</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -2305,18 +2305,18 @@
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="37">
+      <c r="A11" s="31">
         <v>3</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>120</v>
+      <c r="B11" s="26" t="s">
+        <v>119</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="37">
+      <c r="D11" s="31">
         <v>3</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>123</v>
+      <c r="E11" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -2329,7 +2329,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="26"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -2342,126 +2342,126 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="26"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="B14" s="38" t="s">
-        <v>170</v>
+      <c r="B14" s="32" t="s">
+        <v>169</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="26"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="38" t="s">
-        <v>171</v>
+      <c r="B15" s="32" t="s">
+        <v>170</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="26"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="38" t="s">
-        <v>115</v>
+      <c r="B16" s="32" t="s">
+        <v>114</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="26"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
-      <c r="B17" s="38" t="s">
-        <v>172</v>
+      <c r="B17" s="32" t="s">
+        <v>171</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="26"/>
+      <c r="F17" s="21"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
-      <c r="B18" s="38" t="s">
-        <v>116</v>
+      <c r="B18" s="32" t="s">
+        <v>115</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="26"/>
+      <c r="F18" s="21"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
-      <c r="B19" s="38" t="s">
-        <v>173</v>
+      <c r="B19" s="32" t="s">
+        <v>172</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="5"/>
-      <c r="F19" s="26"/>
+      <c r="F19" s="21"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
-      <c r="B20" s="38" t="s">
-        <v>117</v>
+      <c r="B20" s="32" t="s">
+        <v>116</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="26"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="29"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
     </row>
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="5"/>
@@ -2474,10 +2474,10 @@
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="5"/>
@@ -2493,7 +2493,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2508,7 +2508,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2541,7 +2541,7 @@
       <c r="I28" s="5"/>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="5"/>
@@ -2554,10 +2554,10 @@
       <c r="I29" s="5"/>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="5"/>
@@ -2569,11 +2569,11 @@
       <c r="I30" s="5"/>
     </row>
     <row r="31" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B31" s="27" t="s">
         <v>126</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>127</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -2584,11 +2584,11 @@
       <c r="I31" s="5"/>
     </row>
     <row r="32" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="27" t="s">
         <v>128</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>129</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -2599,11 +2599,11 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="27" t="s">
         <v>130</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>131</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -2614,11 +2614,11 @@
       <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="27" t="s">
         <v>132</v>
-      </c>
-      <c r="B34" s="32" t="s">
-        <v>133</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -2640,7 +2640,7 @@
       <c r="I35" s="5"/>
     </row>
     <row r="36" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="5"/>
@@ -2653,13 +2653,13 @@
       <c r="I36" s="5"/>
     </row>
     <row r="37" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="36" t="s">
+      <c r="B37" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="30" t="s">
         <v>47</v>
       </c>
       <c r="D37" s="4"/>
@@ -2670,14 +2670,14 @@
       <c r="I37" s="5"/>
     </row>
     <row r="38" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="27" t="s">
         <v>134</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="5"/>
@@ -2687,14 +2687,14 @@
       <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="C39" s="27" t="s">
         <v>137</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>138</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="5"/>
@@ -2704,14 +2704,14 @@
       <c r="I39" s="5"/>
     </row>
     <row r="40" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="C40" s="27" t="s">
         <v>140</v>
-      </c>
-      <c r="C40" s="32" t="s">
-        <v>141</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="5"/>
@@ -2743,7 +2743,7 @@
       <c r="I42" s="5"/>
     </row>
     <row r="43" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="30" t="s">
+      <c r="A43" s="25" t="s">
         <v>11</v>
       </c>
       <c r="B43" s="5"/>
@@ -2781,226 +2781,226 @@
       <c r="I44" s="5"/>
     </row>
     <row r="45" spans="1:9" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="31" t="s">
+      <c r="D45" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="D45" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" s="31" t="s">
+      <c r="F45" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="F45" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G45" s="31" t="s">
-        <v>66</v>
+      <c r="G45" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="D46" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E46" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="D46" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="E46" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="F46" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G46" s="31" t="s">
-        <v>66</v>
+      <c r="F46" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:9" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="D47" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="D47" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="E47" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>66</v>
+      <c r="F47" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:9" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="C48" s="31" t="s">
+      <c r="D48" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="D48" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="E48" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="F48" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>66</v>
+      <c r="E48" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
     </row>
     <row r="49" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="E49" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>66</v>
+      <c r="D49" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
     </row>
     <row r="50" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="D50" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="D50" s="31" t="s">
+      <c r="E50" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="E50" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="F50" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>66</v>
+      <c r="F50" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C51" s="31" t="s">
+      <c r="D51" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E51" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="D51" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="F51" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>66</v>
+      <c r="F51" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
     </row>
     <row r="52" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" s="31" t="s">
+      <c r="A52" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C52" s="31" t="s">
+      <c r="D52" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="D52" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="E52" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="F52" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G52" s="31" t="s">
-        <v>66</v>
+      <c r="F52" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G52" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
     </row>
     <row r="53" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="31" t="s">
+      <c r="A53" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="D53" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="E53" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="D53" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="E53" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="F53" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G53" s="31" t="s">
-        <v>66</v>
+      <c r="F53" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="G53" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
